--- a/outputs/业务SQL跑通记录.xlsx
+++ b/outputs/业务SQL跑通记录.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>已跑通：用户已确认。未记录：尚未登记最终 SQL，不表示一定没有跑通，也不表示跑不通。</t>
+          <t>已跑通：用户已确认。已跑通（改回UDF后待用户确认）：用户确认过的是旧写法，新写法只在本机执行过。未记录：尚未登记最终 SQL，不表示一定没有跑通，也不表示跑不通。</t>
         </is>
       </c>
     </row>
@@ -645,12 +645,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>已跑通</t>
+          <t>已跑通（改回UDF后待用户确认）</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>三条语句（黑域名、黑文件、黑 URL）均已跑通</t>
+          <t>三条语句此前用户确认已跑通；改回 UDF 写法后待用户确认</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2233,7 @@
           get_json_object(str10_tmp, '$.info.attr') AS attr,
           str2 AS devid
    FROM csc.ods_csc_log_audit,
-        unnest(ifnull(cast(parse_json(regexp_replace(str10, '\\\\+"', '"')) AS ARRAY&lt;JSON&gt;), [])) AS str10_tbl(str10_tmp)
+        unnest(`default`.format_json_list(regexp_replace(str10, '\\\\+"', '"'))) AS str10_tbl(str10_tmp)
    WHERE app_id = 'analysis-proxy-api'
      AND module_id IN ('file_hash', 'file_scan')
      AND str1 IN ('VNGAF', 'NGAF', 'EDR', 'EDR_BOTNET', 'SIP', 'SIP_SMTP', 'SIP_SMB',
@@ -2252,7 +2252,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>已跑通</t>
+          <t>已跑通（改回UDF后待用户确认）</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>用户确认已跑通（2026-10-16）。本机实验库另执行过三条：黑域名 110 行、黑文件 0 行、黑 URL 100 行（outputs/topthreat-hot-stat-results.tsv，ACT-042）。黑文件 0 行是本机造数的 long1 不为 0，不是语句报错。</t>
+          <t>用户确认已跑通的是 parse_json 写法（2026-10-16）。按 DEC-023 改回 format_json_list 后，只在本机 StarRocks 用 UDF 孪生实现执行过（ACT-046）：黑域名 320 行、黑文件 50 行、黑 URL 620 行，数据为合成数据。用户尚未在当前 StarRocks 确认改回后的语句。</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>库表改 csc.ods_csc_log_audit（DEC-014）；log_app_id 改 app_id（DEC-015）；explode(format_json_list()) 改 unnest(parse_json())（ACT-038）；加 SET_VAR(new_planner_optimize_timeout=60000)（DEC-022）。该语句没有 sodl 分支。旧 SQL 写死 day=20250826、hour=01，新语句写 day=20261001、hour=0（实验窗口）。</t>
+          <t>UDF 按 DEC-023 原样保留：`default`.format_json_list 包在 unnest 里，default 是保留字所以加反引号；ACT-038 的 parse_json 写法已撤回。库表改 csc.ods_csc_log_audit（DEC-014）；log_app_id 改 app_id（DEC-015）；explode(UDF) 改 unnest(UDF)；加 SET_VAR(new_planner_optimize_timeout=60000)（DEC-022）。该语句没有 sodl 分支。旧 SQL 写死 day=20250826、hour=01，新语句写 day=20261001、hour=0（实验窗口）。</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
      (SELECT lower(get_json_object(str10_tmp, '$.url')) AS url,
              str2 AS devid
       FROM csc.ods_csc_log_audit,
-           unnest(ifnull(cast(parse_json(regexp_replace(str10, '\\\\+"', '"')) AS ARRAY&lt;JSON&gt;), [])) AS str10_tbl(str10_tmp)
+           unnest(`default`.format_json_list(regexp_replace(str10, '\\\\+"', '"'))) AS str10_tbl(str10_tmp)
       WHERE app_id IN ('url-proxy-svc', 'cloudcheck')
         AND module_id IN ('url-proxy-svc', 'CloudCheck')
         AND str1 IN ('VNGAF', 'NGAF', 'EDR', 'EDR_BOTNET', 'SIP', 'SIP_SMTP', 'SIP_SMB',
@@ -2427,7 +2427,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>已跑通</t>
+          <t>已跑通（改回UDF后待用户确认）</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2437,12 +2437,12 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>用户确认已跑通（2026-10-16）。本机实验库另执行过三条：黑域名 110 行、黑文件 0 行、黑 URL 100 行（outputs/topthreat-hot-stat-results.tsv，ACT-042）。黑文件 0 行是本机造数的 long1 不为 0，不是语句报错。</t>
+          <t>用户确认已跑通的是 parse_json 写法（2026-10-16）。按 DEC-023 改回 format_json_list 后，只在本机 StarRocks 用 UDF 孪生实现执行过（ACT-046）：黑域名 320 行、黑文件 50 行、黑 URL 620 行，数据为合成数据。用户尚未在当前 StarRocks 确认改回后的语句。</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>改写项同 black_domain_stat：库表、app_id、sodl 时间条件、count(1)、deviceId、unnest(parse_json())、规划超时提示；${day}/${hour} 写死为实验窗口 20261001 / 0。</t>
+          <t>UDF 按 DEC-023 原样保留：`default`.format_json_list 包在 unnest 里，default 是保留字所以加反引号；ACT-038 的 parse_json 写法已撤回。改写项同 black_domain_stat：库表、app_id、sodl 时间条件、count(1)、deviceId、unnest(UDF)、规划超时提示；${day}/${hour} 写死为实验窗口 20261001 / 0。</t>
         </is>
       </c>
     </row>
@@ -2567,7 +2567,7 @@
      (SELECT lower(get_json_object(str10_tmp, '$.domain')) AS domain,
              str2 AS devid
       FROM csc.ods_csc_log_audit,
-           unnest(ifnull(cast(parse_json(regexp_replace(str10, '\\\\+"', '"')) AS ARRAY&lt;JSON&gt;), [])) AS str10_tbl(str10_tmp)
+           unnest(`default`.format_json_list(regexp_replace(str10, '\\\\+"', '"'))) AS str10_tbl(str10_tmp)
       WHERE app_id IN ('domain-proxy-svc', 'cloudcheck')
         AND module_id IN ('domain-proxy-svc', 'CloudCheck')
         AND str1 IN ('VNGAF', 'NGAF', 'EDR', 'EDR_BOTNET', 'SIP', 'SIP_SMTP', 'SIP_SMB',
@@ -2613,7 +2613,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>已跑通</t>
+          <t>已跑通（改回UDF后待用户确认）</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>用户确认已跑通（2026-10-16）。本机实验库另执行过三条：黑域名 110 行、黑文件 0 行、黑 URL 100 行（outputs/topthreat-hot-stat-results.tsv，ACT-042）。黑文件 0 行是本机造数的 long1 不为 0，不是语句报错。</t>
+          <t>用户确认已跑通的是 parse_json 写法（2026-10-16）。按 DEC-023 改回 format_json_list 后，只在本机 StarRocks 用 UDF 孪生实现执行过（ACT-046）：黑域名 320 行、黑文件 50 行、黑 URL 620 行，数据为合成数据。用户尚未在当前 StarRocks 确认改回后的语句。</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>库表 default.log_audit_source 改 csc.ods_csc_log_audit（DEC-014）；log_app_id 改 app_id（DEC-015）；sodl 的 day/hour 改 insertdate='2026-10-01' 与 hour(from_unixtime(inserttimestamp))=0（DEC-016/017）；sum(log_num) 改 count(1)（DEC-020）；MANAGE/manage 改 deviceId（DEC-021）；LATERAL VIEW explode(format_json_list()) 改 unnest(parse_json())，size()-1 改 cardinality()，数组下标改 1 起（ACT-038）；加 SET_VAR(new_planner_optimize_timeout=60000)（DEC-022）；${day}/${hour} 写死为实验窗口 20261001 / 0。</t>
+          <t>UDF 按 DEC-023 原样保留：`default`.format_json_list 包在 unnest 里，default 是保留字所以加反引号；ACT-038 的 parse_json 写法已撤回。库表 default.log_audit_source 改 csc.ods_csc_log_audit（DEC-014）；log_app_id 改 app_id（DEC-015）；sodl 的 day/hour 改 insertdate='2026-10-01' 与 hour(from_unixtime(inserttimestamp))=0（DEC-016/017）；sum(log_num) 改 count(1)（DEC-020）；MANAGE/manage 改 deviceId（DEC-021）；LATERAL VIEW explode(UDF) 改 unnest(UDF)，size()-1 改 cardinality()，数组下标改 1 起；加 SET_VAR(new_planner_optimize_timeout=60000)（DEC-022）；${day}/${hour} 写死为实验窗口 20261001 / 0。</t>
         </is>
       </c>
     </row>

--- a/outputs/业务SQL跑通记录.xlsx
+++ b/outputs/业务SQL跑通记录.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>目前只有热门威胁已记录，来自 outputs/topthreat-hot-stat-starrocks.sql（位于 cursor/sr-convert-all-sql-02a9 分支）。</t>
+          <t>目前只有热门威胁已记录，来自 outputs/topthreat-hot-stat-starrocks.sql（位于 cursor/sr-convert-all-sql-02a9 分支）。 2026-10-19 起另有 ip-security-log-etl-prc，最终 SQL 见 outputs/migratable-tasks-starrocks.sql 或本表对应行。</t>
         </is>
       </c>
     </row>
@@ -677,14 +677,18 @@
         <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>未记录</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>已跑通</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>用户 2026-10-19 确认执行通过；详见 ACT-051</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -4700,15 +4704,42 @@
 limit 100000</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="4" t="inlineStr">
-        <is>
-          <t>未记录</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr"/>
-      <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>SELECT distinct dstip
+FROM sodl.network_security_log
+WHERE insertdate = '2026-10-01'
+    AND regexp_extract(dstip, '^((0\\.0\\.0\\.0)|(127\\.0\\.0\\.1)|(localhost)|(10\\.)|(172\\.1[6-9]\\.)|(172\\.2[0-9]\\.)|(172\\.3[0-1]\\.)|(192\\.168\\.))', 1) = ''
+    AND regexp_extract(dstip, '^(\\d{1,3}\\.\\d{1,3}\\.\\d{1,3}\\.\\d{1,3})$', 1) != ''
+    AND engine not in ('premise_ioc', 'cloud_ioc', 'sase_ioc')
+    AND severity &gt; 50
+    AND (threatclass in (209, 208, 216, 214,  203, 40)
+        OR concat_ws('-', cast(threatclass as String),
+                          cast(threattype as String),
+                          cast(threatsubtype as String)) = '212-10-0')
+limit 100000;</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>已跑通</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>用户 2026-10-19 回复“ip-security-log-etl-prc 这个执行通过”。执行环境、行数、耗时未提供。此前本机 StarRocks 合成数据验证见 ACT-050（258 行，与 Python 独立计算一致）。</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>sodl.network_security_log 缺少新平台表名，保留原名；DAY=20261001 改 insertdate='2026-10-01'（DEC-016）；regexp_extract 两参数补组号 1；日期是实验窗口，不是调度参数；severity、threatclass 的数值比较未加 CAST（DEC-009）。</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">

--- a/outputs/业务SQL跑通记录.xlsx
+++ b/outputs/业务SQL跑通记录.xlsx
@@ -1124,15 +1124,21 @@
       <c r="E17" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>未记录</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>已跑通</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>用户 2026-10-19 确认执行通过；详见 ACT-053</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4261,15 +4267,49 @@
 GROUP BY DOMAIN</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>未记录</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>SELECT DOMAIN,
+       array_agg(DISTINCT producttype) AS producttype_list,
+       array_agg(DISTINCT CONCAT(CAST(threatclass AS STRING), '-', CAST(threattype AS STRING),
+       '-', CAST(threatsubtype AS STRING))) AS type_list,
+       array_sort(array_agg(DISTINCT engine)) AS engine_list,
+       COUNT(DISTINCT engine) AS engine_num
+FROM
+  (SELECT regexp_extract(url, '^(?:https?://)?(?:www\\.)?([^/]+)', 1) AS DOMAIN,
+          *
+   FROM sodl.network_security_log
+   WHERE insertdate = '2026-10-01'
+     AND engine NOT IN ('premise_ioc', 'cloud_ioc', 'sase_ioc')
+     AND severity &gt; 50
+     AND (threatclass IN (209, 208, 216, 214, 203, 40)
+          OR CONCAT(CAST(threatclass AS STRING), '-', CAST(threattype AS STRING), '-',
+          CAST(threatsubtype AS STRING)) = '212-10-0')
+     AND action = 2) s
+WHERE NOT (DOMAIN REGEXP '\\d+\\.\\d+\\.\\d+\\.\\d+$' OR DOMAIN REGEXP ':')
+GROUP BY DOMAIN;</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>已跑通</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>用户 2026-10-19 回复“domain-security-log-etl-prc 这个执行通过”。执行环境、行数、耗时未提供。此前本机合成数据执行 ok（ACT-052，临时库 mig_lab）。不等于已切流或等价对账通过；日期是实验窗口。详见 ACT-053</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>DEC-016 日期；方言：collect_set 改为 array_agg(DISTINCT ...)，sort_array 改为 array_sort，rlike 改为 REGEXP，反斜杠加倍；DEC-009：severity &gt; 50、action = 2、threatclass in (...) 的比较需要按实际编码转换，未加 CAST</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -4307,15 +4347,31 @@
           <t>SELECT 1 FROM sodl.network_security_log WHERE day=:mday LIMIT 1</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>未记录</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>SELECT 1 FROM sodl.network_security_log WHERE insertdate = '2026-10-01' LIMIT 1;</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>已跑通</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>用户 2026-10-19 回复“domain-security-log-etl-prc 这个执行通过”。执行环境、行数、耗时未提供。此前本机合成数据执行 ok（ACT-052，临时库 mig_lab）。不等于已切流或等价对账通过；日期是实验窗口。详见 ACT-053</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>DEC-016：day=20261001 改为 insertdate = '2026-10-01'</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">

--- a/outputs/业务SQL跑通记录.xlsx
+++ b/outputs/业务SQL跑通记录.xlsx
@@ -645,12 +645,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>已跑通（改回UDF后待用户确认）</t>
+          <t>已跑通</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>三条语句此前用户确认已跑通；改回 UDF 写法后待用户确认</t>
+          <t>用户 2026-10-19 确认 UDF 写法也执行通过；详见 ACT-054</t>
         </is>
       </c>
     </row>
@@ -2262,17 +2262,17 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>已跑通（改回UDF后待用户确认）</t>
+          <t>已跑通</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>用户确认已跑通的是 parse_json 写法（2026-10-16）。按 DEC-023 改回 format_json_list 后，只在本机 StarRocks 用 UDF 孪生实现执行过（ACT-046）：黑域名 320 行、黑文件 50 行、黑 URL 620 行，数据为合成数据。用户尚未在当前 StarRocks 确认改回后的语句。</t>
+          <t>用户 2026-10-19 回复“热门威胁也运行通过”，确认 DEC-023 改回 format_json_list 的 UDF 写法在其 StarRocks 执行通过。此前 2026-10-16 已确认 parse_json 写法跑通。执行环境、行数、耗时未提供；本机合成数据结果见 ACT-046、ACT-052。详见 ACT-054</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2437,17 +2437,17 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>已跑通（改回UDF后待用户确认）</t>
+          <t>已跑通</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>用户确认已跑通的是 parse_json 写法（2026-10-16）。按 DEC-023 改回 format_json_list 后，只在本机 StarRocks 用 UDF 孪生实现执行过（ACT-046）：黑域名 320 行、黑文件 50 行、黑 URL 620 行，数据为合成数据。用户尚未在当前 StarRocks 确认改回后的语句。</t>
+          <t>用户 2026-10-19 回复“热门威胁也运行通过”，确认 DEC-023 改回 format_json_list 的 UDF 写法在其 StarRocks 执行通过。此前 2026-10-16 已确认 parse_json 写法跑通。执行环境、行数、耗时未提供；本机合成数据结果见 ACT-046、ACT-052。详见 ACT-054</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2623,17 +2623,17 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>已跑通（改回UDF后待用户确认）</t>
+          <t>已跑通</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>用户确认已跑通的是 parse_json 写法（2026-10-16）。按 DEC-023 改回 format_json_list 后，只在本机 StarRocks 用 UDF 孪生实现执行过（ACT-046）：黑域名 320 行、黑文件 50 行、黑 URL 620 行，数据为合成数据。用户尚未在当前 StarRocks 确认改回后的语句。</t>
+          <t>用户 2026-10-19 回复“热门威胁也运行通过”，确认 DEC-023 改回 format_json_list 的 UDF 写法在其 StarRocks 执行通过。此前 2026-10-16 已确认 parse_json 写法跑通。执行环境、行数、耗时未提供；本机合成数据结果见 ACT-046、ACT-052。详见 ACT-054</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">

--- a/outputs/业务SQL跑通记录.xlsx
+++ b/outputs/业务SQL跑通记录.xlsx
@@ -904,15 +904,21 @@
       <c r="E10" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>未记录</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>已跑通（3/6，BY_DEVICE 3 条未转换）</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>用户 2026-10-19 确认跑成功，范围为 3 条非设备语句；详见 ACT-055</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -3799,15 +3805,39 @@
 GROUP BY queries</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>未记录</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>SELECT queries as domain,
+       count(1) AS num
+FROM sodl.dns_log
+WHERE insertdate = '2026-10-01'
+  AND producttype in ('AF', 'NGAF', 'VNGAF')
+  AND qr=0
+  AND length(queries) &gt; 3
+  AND locate('.', queries) != 0
+GROUP BY queries;</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>已跑通</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>用户 2026-10-19 回复“top-visit-host-produce-job 跑成功”。按本任务已转换的 3 条非设备语句登记；执行环境、行数、耗时未提供。此前本机合成数据执行 ok（ACT-052）。不等于已切流或等价对账通过；日期是实验窗口。详见 ACT-055</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>DEC-016：day = 20261001 改为 insertdate = '2026-10-01'；DEC-020：sodl 没有 log_num，sum(log_num) 改为 count(1)；DEC-009：qr=0、length(queries) &gt; 3 的比较需要按实际编码转换，未加 CAST</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3861,7 +3891,11 @@
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>未转换：all.sql 头部写明运行路径 need_device=False 只用非设备版，BY_DEVICE 变体未转 StarRocks，也未执行；详见 ACT-055</t>
+        </is>
+      </c>
       <c r="L34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
@@ -3917,15 +3951,48 @@
 LIMIT 500000</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>未记录</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>with ip_stat as (
+SELECT concat(split(ip, '.')[1], '.', split(ip, '.')[2], '.', split(ip, '.')[3]) AS c_segment
+FROM
+    (SELECT get_json_object(replace(str4, '\\', ''), '$[*].ip') AS ip_list
+      FROM csc.ods_csc_log_audit
+      WHERE day = 20261001
+        AND app_id='ip-proxy-svc'
+        AND module_id='ip-proxy-svc'
+        AND str1='NGAF'
+        AND str5='[cf]') s
+   , unnest(split(regexp_replace(ip_list, '\\[|\\]|\\"', ''), ',')) AS exploded_table(ip)
+   WHERE locate('.', ip) != 0
+)
+SELECT c_segment as ip,
+       count(1) as num
+FROM ip_stat
+GROUP BY c_segment
+LIMIT 500000;</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>已跑通</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>用户 2026-10-19 回复“top-visit-host-produce-job 跑成功”。按本任务已转换的 3 条非设备语句登记；执行环境、行数、耗时未提供。此前本机合成数据执行 ok（ACT-052）。不等于已切流或等价对账通过；日期是实验窗口。详见 ACT-055</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>DEC-014 表名；DEC-015 log_app_id 改为 app_id；csc.ods_csc_log_audit 的 day、module_id、str1、str4、str5 缺少新平台字段名，保留旧名；方言：LATERAL VIEW explode 改为 unnest；Hive 数组下标从 0 起，StarRocks 从 1 起；split 的分隔符在 StarRocks 是字面量，'\.' 改为 '.'；get_json_object 的 '$[*].ip' 路径在 StarRocks 是否返回与 Hive 相同的数组字符串，需在目标环境核对</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3986,7 +4053,11 @@
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
-      <c r="K36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>未转换：all.sql 头部写明运行路径 need_device=False 只用非设备版，BY_DEVICE 变体未转 StarRocks，也未执行；详见 ACT-055</t>
+        </is>
+      </c>
       <c r="L36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
@@ -4032,15 +4103,38 @@
 GROUP BY host</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>未记录</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>SELECT host,
+       count(1) AS num
+FROM sodl.url_log
+WHERE insertdate = '2026-10-01'
+  AND host is not null
+  AND locate('.', host)  != 0
+  AND producttype in ('AF', 'NGAF', 'VNGAF')
+GROUP BY host;</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>已跑通</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>用户 2026-10-19 回复“top-visit-host-produce-job 跑成功”。按本任务已转换的 3 条非设备语句登记；执行环境、行数、耗时未提供。此前本机合成数据执行 ok（ACT-052）。不等于已切流或等价对账通过；日期是实验窗口。详见 ACT-055</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>DEC-016 日期；DEC-020 sum(log_num) 改为 count(1)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -4093,7 +4187,11 @@
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>未转换：all.sql 头部写明运行路径 need_device=False 只用非设备版，BY_DEVICE 变体未转 StarRocks，也未执行；详见 ACT-055</t>
+        </is>
+      </c>
       <c r="L38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
